--- a/Documents/LeadDesk_Task_A_B_Branch_Plan.xlsx
+++ b/Documents/LeadDesk_Task_A_B_Branch_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DigitHero_ShwetalShah\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F908B549-772C-43CF-BBA2-7DDDF16AA917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43023DD8-725F-491E-B20A-72D2272485A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1207,6 +1207,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1625600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{752F3774-45DB-B98B-AB3E-243A28C90BD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1625600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06E0BBB5-1AE7-6B10-04BC-3C35FB96E60B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1254,6 +1362,114 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1625600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C39F58F-0650-E99F-3EC3-E894FCB3AB11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1625600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8387D3A6-ED1B-84B2-CF75-BEE935D3DEFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
